--- a/accountant-skill/data/input/journals/purchases_journal.xlsx
+++ b/accountant-skill/data/input/journals/purchases_journal.xlsx
@@ -520,7 +520,7 @@
         </is>
       </c>
       <c r="E2" s="3" t="n">
-        <v>50000</v>
+        <v>50010</v>
       </c>
       <c r="F2" s="3" t="n">
         <v>20000</v>
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>50000</v>
+        <v>50010</v>
       </c>
       <c r="F3" s="3" t="n">
         <v>20000</v>
@@ -602,7 +602,7 @@
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>50100</v>
+        <v>50110</v>
       </c>
       <c r="F4" s="3" t="n">
         <v>20000</v>
@@ -643,7 +643,7 @@
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>50000</v>
+        <v>50010</v>
       </c>
       <c r="F5" s="3" t="n">
         <v>20000</v>
@@ -684,7 +684,7 @@
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>50000</v>
+        <v>50010</v>
       </c>
       <c r="F6" s="3" t="n">
         <v>20000</v>
@@ -725,7 +725,7 @@
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>50100</v>
+        <v>50110</v>
       </c>
       <c r="F7" s="3" t="n">
         <v>20000</v>
@@ -766,7 +766,7 @@
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>50000</v>
+        <v>50010</v>
       </c>
       <c r="F8" s="3" t="n">
         <v>20000</v>
@@ -807,7 +807,7 @@
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>50000</v>
+        <v>50010</v>
       </c>
       <c r="F9" s="3" t="n">
         <v>20000</v>
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>50000</v>
+        <v>50010</v>
       </c>
       <c r="F10" s="3" t="n">
         <v>20000</v>
@@ -889,7 +889,7 @@
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>50100</v>
+        <v>50110</v>
       </c>
       <c r="F11" s="3" t="n">
         <v>20000</v>
